--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -68,7 +68,7 @@
     <t>Damage</t>
   </si>
   <si>
-    <t>enemy</t>
+    <t>Enemy</t>
   </si>
   <si>
     <r>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>strike+</t>
-  </si>
-  <si>
-    <t>Enemy</t>
   </si>
   <si>
     <r>
@@ -493,21 +490,21 @@
     <font>
       <sz val="11.5"/>
       <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1578,49 +1575,49 @@
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:5">
       <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1">
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>12</v>
@@ -1629,15 +1626,15 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" ht="16.2" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -1646,78 +1643,78 @@
         <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:5">
       <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.2" spans="1:5">
       <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -44,12 +44,12 @@
     <t>#Description</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>类型</t>
   </si>
   <si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>描述</t>
-  </si>
-  <si>
-    <t>strike</t>
   </si>
   <si>
     <t>Damage</t>
@@ -92,9 +89,6 @@
     </r>
   </si>
   <si>
-    <t>strike+</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -126,9 +120,6 @@
     </r>
   </si>
   <si>
-    <t>defend</t>
-  </si>
-  <si>
     <t>Block</t>
   </si>
   <si>
@@ -164,15 +155,6 @@
       </rPr>
       <t>点格挡。</t>
     </r>
-  </si>
-  <si>
-    <t>defend+</t>
-  </si>
-  <si>
-    <t>heavy_blow</t>
-  </si>
-  <si>
-    <t>heavy_blow+</t>
   </si>
   <si>
     <r>
@@ -215,9 +197,6 @@
     </r>
   </si>
   <si>
-    <t>tactics</t>
-  </si>
-  <si>
     <t>DrawCard</t>
   </si>
   <si>
@@ -250,12 +229,6 @@
       </rPr>
       <t>张牌。</t>
     </r>
-  </si>
-  <si>
-    <t>tactics+</t>
-  </si>
-  <si>
-    <t>empower</t>
   </si>
   <si>
     <t>GainEnergy</t>
@@ -289,9 +262,6 @@
       </rPr>
       <t>点能量。</t>
     </r>
-  </si>
-  <si>
-    <t>empower+</t>
   </si>
   <si>
     <r>
@@ -490,7 +460,7 @@
     <font>
       <sz val="11.5"/>
       <color rgb="FF0F1115"/>
-      <name val="宋体"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -498,13 +468,13 @@
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.5"/>
       <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1518,16 +1488,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1548,173 +1518,173 @@
       </c>
     </row>
     <row r="4" ht="15" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="5" ht="15" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
+      <c r="A5" s="1">
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" s="1">
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
+      <c r="A7" s="1">
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
+      <c r="A8" s="1">
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="16.2" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
+      <c r="A9" s="1">
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1">
         <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
+      <c r="A10" s="1">
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:5">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" ht="15" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" ht="16.2" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>29</v>
+      <c r="A12" s="1">
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
+      <c r="A13" s="1">
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
-    <sheet name="CardEffects" sheetId="1" r:id="rId1"/>
+    <sheet name="CardEffectsConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,21 +27,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>EffectType</t>
-  </si>
-  <si>
-    <t>Value</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Type</t>
   </si>
   <si>
     <t>Target</t>
   </si>
   <si>
-    <t>#Description</t>
+    <t>Description</t>
   </si>
   <si>
     <t>int</t>
@@ -51,9 +48,6 @@
   </si>
   <si>
     <t>类型</t>
-  </si>
-  <si>
-    <t>效果值</t>
   </si>
   <si>
     <t>目标</t>
@@ -77,37 +71,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>造成{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点伤害。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>造成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{0}</t>
     </r>
     <r>
       <rPr>
@@ -157,46 +120,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>造成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点伤害。</t>
-    </r>
-  </si>
-  <si>
     <t>DrawCard</t>
   </si>
   <si>
@@ -248,36 +171,6 @@
       <rPr>
         <sz val="11.5"/>
         <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> {0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点能量。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>获得</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -305,7 +198,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,21 +353,15 @@
     <font>
       <sz val="11.5"/>
       <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.5"/>
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1459,14 +1346,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="15.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1479,255 +1366,126 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="4" ht="15" spans="1:5">
+    <row r="4" ht="15" spans="1:4">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="5" ht="15" spans="1:5">
+    <row r="5" ht="15" spans="1:4">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="1:5">
+    <row r="6" ht="15" spans="1:4">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1">
-        <v>5</v>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="7" ht="15" spans="1:5">
+    <row r="7" ht="15" spans="1:4">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1">
-        <v>8</v>
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:5">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
     </row>
-    <row r="9" ht="16.2" spans="1:5">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1">
-        <v>16</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>18</v>
-      </c>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
-    <row r="10" ht="15" spans="1:5">
-      <c r="A10" s="1">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
     </row>
-    <row r="11" ht="15" spans="1:5">
-      <c r="A11" s="1">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="1">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="11" ht="13" customHeight="1" spans="1:4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
     </row>
-    <row r="12" ht="16.2" spans="1:5">
-      <c r="A12" s="1">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>22</v>
-      </c>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
     </row>
-    <row r="13" ht="15" spans="1:5">
-      <c r="A13" s="1">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="1">
-        <v>2</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C829B1B-E935-4938-9E7F-7DE8E4B606FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03238DE9-7AA4-4B37-B1C9-8ED5EC3096E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -203,6 +201,14 @@
       </rPr>
       <t>点能量。</t>
     </r>
+  </si>
+  <si>
+    <t>vulnerable</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>给敌人添加{0}层易伤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -270,8 +276,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -860,6 +869,20 @@
         <v>18</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="11" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03238DE9-7AA4-4B37-B1C9-8ED5EC3096E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9C4061-B34F-42B0-AC34-6DB8FB95B5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardEffectsConfig" sheetId="1" r:id="rId1"/>
@@ -203,12 +203,11 @@
     </r>
   </si>
   <si>
-    <t>vulnerable</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>给敌人添加{0}层易伤</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vulnerable</t>
   </si>
 </sst>
 </file>
@@ -276,11 +275,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -873,14 +869,14 @@
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
+      <c r="B8" t="s">
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>20</v>
+      <c r="D8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/CardEffects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9C4061-B34F-42B0-AC34-6DB8FB95B5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE07437-606C-42AF-A586-683AB2C3F4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardEffectsConfig" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>Id</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>描述</t>
-  </si>
-  <si>
-    <t>Damage</t>
   </si>
   <si>
     <t>Enemy</t>
@@ -208,6 +205,18 @@
   </si>
   <si>
     <t>Vulnerable</t>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageSelf</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>失去{0}点生命</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -275,8 +284,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -813,14 +825,14 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.25">
@@ -828,13 +840,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.25">
@@ -842,13 +854,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.25">
@@ -856,13 +868,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
         <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -870,13 +882,27 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.25"/>
